--- a/ig/ch-elm/StructureDefinition-ch-elm-quantity-arbu.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-quantity-arbu.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -348,7 +348,7 @@
     <t>uncertainty</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-uncertainty}
+    <t xml:space="preserve">Extension {iso21090-uncertainty|5.3.0}
 </t>
   </si>
   <si>
@@ -370,7 +370,7 @@
     <t>uncertaintyType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-uncertaintyType}
+    <t xml:space="preserve">Extension {iso21090-uncertaintyType|5.3.0}
 </t>
   </si>
   <si>
@@ -846,7 +846,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="31.77734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="36.30859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/ch-elm/StructureDefinition-ch-elm-quantity-arbu.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-quantity-arbu.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-quantity-arbu.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-quantity-arbu.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-quantity-arbu.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-quantity-arbu.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
